--- a/docs/files/pnl_2026.xlsx
+++ b/docs/files/pnl_2026.xlsx
@@ -20,7 +20,6 @@
     <sheet name="2026-10" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="2026-11" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2026-12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Royalty Map" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,24 +434,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wenzl SimBand LLC — P&amp;L YTD 2026</t>
+          <t>Fly Asshole LLC (FICTIONAL DEMO BAND) — P&amp;L YTD 2026</t>
         </is>
       </c>
     </row>
@@ -474,203 +473,298 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25238.72</v>
+        <v>7213.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Publishing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18605.69</v>
+        <v>3222.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Sync licensing</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1941.46</v>
+        <v>5299.98</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45785.87</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Other royalties</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2869.79</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>— EXPENSES —</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Live shows</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>25238.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4114.88</v>
+        <v>1941.46</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>276</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45785.87</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Contractor - Business</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>96.81999999999999</v>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>— EXPENSES —</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Contract Labor - Music</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>160.68</v>
+        <v>4114.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Music &amp; Distribution Software</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178.87</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Contractor - Business</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>263.76</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Contract Labor - Music</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1280.11</v>
+        <v>160.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>379.16</v>
+        <v>178.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gear &amp; Production</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>604.49</v>
+        <v>263.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>648</v>
+        <v>1280.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Video Production</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3479.57</v>
+        <v>379.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Gear &amp; Production</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>240</v>
+        <v>604.49</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>11722.34</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>648</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>34063.53</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Video Production</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3479.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4853.88</v>
-      </c>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>11722.34</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>34063.53</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>— SCHEDULE C BRIDGE (SIMULATED) —</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Books net profit (above)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>34063.53</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>+ Meals add-back (only 50% of meals is deductible)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>189.58</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <f> Taxable net (Schedule C line 31)</f>
+        <v/>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>34253.11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Self-employment tax (15.3% on 92.35% of net)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4839.81</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly set-aside = net × 0.25 ÷ 4</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2140.82</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    = $34,253.11 × 0.25 ÷ 4 = $2,140.82</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (covers self-employment tax + a cushion toward income tax — SIMULATION, not advice)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -683,17 +777,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -722,172 +816,194 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2027.44</v>
+        <v>587.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Publishing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3255.94</v>
+        <v>944.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Sync licensing</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>207.1</v>
+        <v>1348.17</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>5490.48</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Other royalties</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>375.82</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>— EXPENSES —</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Live shows</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2027.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1136.91</v>
+        <v>207.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>23</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5490.48</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Contractor - Business</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>96.81999999999999</v>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>— EXPENSES —</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Music &amp; Distribution Software</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12.99</v>
+        <v>1136.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.98</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Contractor - Business</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>51.7</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gear &amp; Production</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>123.64</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>1541.04</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gear &amp; Production</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>123.64</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>3949.44</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>404.49</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1541.04</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3949.44</v>
       </c>
     </row>
   </sheetData>
@@ -901,17 +1017,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -940,172 +1056,184 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3175.66</v>
+        <v>834.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Sync licensing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2296.05</v>
+        <v>1278.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Other royalties</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>182.83</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Live shows</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3175.66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Merch — online</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>115.98</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>5587.69</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>— EXPENSES —</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Meta Ads</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>186.81</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>23</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Music &amp; Distribution Software</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.99</v>
+        <v>186.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.98</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>250.04</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>35</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gear &amp; Production</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46.98</v>
+        <v>250.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Gear &amp; Production</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>46.98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B21" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>650.8</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>4936.89</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -1119,17 +1247,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -1158,162 +1286,174 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>565.9400000000001</v>
+        <v>895.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Publishing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1245.03</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Other royalties</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>300.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Live shows</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>565.9400000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Merch — online</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>247</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>2057.97</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>— EXPENSES —</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Music &amp; Distribution Software</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>12.99</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.98</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24.35</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gear &amp; Production</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>193.53</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Video Production</t>
+          <t>Gear &amp; Production</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>334.35</v>
+        <v>193.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Video Production</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>334.35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B20" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>684.2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>1373.77</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -1327,17 +1467,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -1366,562 +1506,184 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3035.08</v>
+        <v>741.6900000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Publishing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2826.96</v>
+        <v>831.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Sync licensing</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>138.21</v>
+        <v>1086.96</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>6000.25</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Other royalties</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>167.08</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>— EXPENSES —</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Live shows</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3035.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>138.21</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Music &amp; Distribution Software</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>12.99</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>6000.25</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software &amp; Subscriptions</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>21.98</v>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>— EXPENSES —</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63.22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.57</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gear &amp; Production</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116.56</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>63.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>336.32</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gear &amp; Production</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>116.56</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>5663.93</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>404.49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real royalties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Royalty Map — simulated YTD 2026 (net dollars per collector)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>— COMPOSITION SIDE (songwriter/publisher) —</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>— RECORDING SIDE (artist/master owner) —</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>ASCAP-sim (PRO)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Songtrust-sim (pub admin, 15%)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>HFA-sim (mechanicals, 11.5%, 4-8mo)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Distributor-sims (DistroKid/Symphonic)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>SoundExchange-sim</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Direct-to-band</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Row total</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Interactive streaming (Spotify etc.)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>478.54</v>
-      </c>
-      <c r="C6" t="n">
-        <v>610.17</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7586.92</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8675.629999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Non-interactive (satellite / web radio)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>74.15000000000001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>396.59</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>470.74</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Public performance — US (radio, venues)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1419.27</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1419.27</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Public performance — international</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>409.93</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>261.33</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>671.26</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Digital downloads</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>133.58</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1379.97</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1513.55</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Syncs (film / ad / game licenses)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2435.13</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2864.85</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5299.98</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Physical (vinyl / CD pressings)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>22.26</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2429.05</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2451.31</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Video (YouTube ad revenue)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>146.95</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>809.7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>956.65</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL (net, YTD)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1971.96</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>3602.18</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>155.84</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>9776.59</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>657.92</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>5293.9</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>21458.39</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Reconciliation (to the penny)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Matrix total (net, all statements issued)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21458.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  landed in checking this year</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>18605.69</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  still in transit (statement issued, payout after year end)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2852.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>US quirk: terrestrial radio pays the songwriter but NOT the recording artist — the recording side of this row is $0 by law.</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>336.32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>5663.93</v>
       </c>
     </row>
   </sheetData>
@@ -1935,17 +1697,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -1974,11 +1736,12 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2001,6 +1764,7 @@
           <t>— EXPENSES —</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2100,16 +1864,6 @@
       </c>
       <c r="B18" s="2" t="n">
         <v>-603.11</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -2123,17 +1877,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -2162,11 +1916,12 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Live shows</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2176,7 +1931,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2199,6 +1954,7 @@
           <t>— EXPENSES —</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2308,16 +2064,6 @@
       </c>
       <c r="B20" s="2" t="n">
         <v>726.48</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -2331,17 +2077,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -2370,31 +2116,32 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Other royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3861.62</v>
+        <v>240.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Live shows</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>240.94</v>
+        <v>3861.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2417,6 +2164,7 @@
           <t>— EXPENSES —</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2506,16 +2254,6 @@
       </c>
       <c r="B19" s="2" t="n">
         <v>3690.44</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -2529,17 +2267,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -2568,31 +2306,32 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1553.36</v>
+        <v>323.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Live shows</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>323.97</v>
+        <v>1553.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Merch — online</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2615,6 +2354,7 @@
           <t>— EXPENSES —</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2734,16 +2474,6 @@
       </c>
       <c r="B22" s="2" t="n">
         <v>1318.05</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -2757,17 +2487,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -2796,152 +2526,164 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2242.17</v>
+        <v>892.1799999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Sync licensing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3123.42</v>
+        <v>1586.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Other royalties</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>645.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Live shows</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2242.17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Merch — online</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>207.7</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>5573.29</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>— EXPENSES —</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Music &amp; Distribution Software</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>12.99</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.98</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50.48</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Video Production</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>917.63</v>
+        <v>50.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Video Production</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>917.63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B19" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>1100.08</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>4473.21</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -2955,17 +2697,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -2994,162 +2736,174 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2692.17</v>
+        <v>875.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Publishing</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1397.63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Other royalties</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>419.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Merch — online</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>155.35</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>2847.52</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>— EXPENSES —</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Meta Ads</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>411.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>23</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Music &amp; Distribution Software</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12.99</v>
+        <v>411.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.98</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62.6</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26.29</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Video Production</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1018.25</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Video Production</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1018.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B20" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>1650.31</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>1197.21</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -3166,14 +2920,14 @@
   <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -3202,172 +2956,174 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2115.47</v>
+        <v>1049.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Other royalties</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1083.4</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Live shows</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2115.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Merch — online</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>92.26000000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>3291.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3291.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>— EXPENSES —</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Meta Ads</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>307.59</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>307.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Music &amp; Distribution Software</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.99</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.98</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49.75</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>47.08</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Meals</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Video Production</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>525.58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Video Production</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>525.58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>1061.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1061.97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>2229.16</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
@@ -3384,14 +3140,14 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIMULATION — bandsim sandbox. Not real money. Not real books.</t>
+          <t>SIMULATION — bandsim sandbox. Not real money. Not real books. Fictional demo band.</t>
         </is>
       </c>
     </row>
@@ -3420,162 +3176,164 @@
           <t>— INCOME —</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Performance - Private Event</t>
+          <t>Streaming royalties</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4321.92</v>
+        <v>1012.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Music Royalties</t>
+          <t>Other royalties</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1517.81</v>
+        <v>505.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merch Sales</t>
+          <t>Live shows</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4321.92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Merch — online</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>185.83</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>6025.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>6025.56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>— EXPENSES —</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Meta Ads</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>555.04</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>555.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Contract Labor - Music</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>160.68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Music &amp; Distribution Software</t>
+          <t>Contract Labor - Music</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12.99</v>
+        <v>160.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Music &amp; Distribution Software</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.98</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>69.81</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>20</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>917.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>917.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>5108.06</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>(Personal spending — excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>404.49</v>
       </c>
     </row>
   </sheetData>
